--- a/data/BASES/PROVEEDORES.xlsx
+++ b/data/BASES/PROVEEDORES.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="121">
   <si>
     <t>RFC</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>DSA</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -899,7 +902,7 @@
         <v>88</v>
       </c>
       <c r="L2" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
